--- a/marketing-kit/plan/launch-checklist-kpi-tracker.xlsx
+++ b/marketing-kit/plan/launch-checklist-kpi-tracker.xlsx
@@ -1067,7 +1067,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Legend: yellow cells are for you to fill in (Owner, Due, Status, Notes). Status drop-down drives the progress line above.</t>
+          <t>Legend: yellow cells are for you to fill in (Owner, Due, Status, Notes). Type Not started, In progress, Done, or Skipped in the Status column; it drives the progress line above.</t>
         </is>
       </c>
     </row>
@@ -1080,11 +1080,6 @@
       <formula>"In progress"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="E6:E28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Not started,In progress,Done,Skipped"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
